--- a/data/trans_dic/P19C02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,23; 39,98</t>
+          <t>30,31; 40,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,26; 46,86</t>
+          <t>36,23; 47,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,07; 55,53</t>
+          <t>44,87; 55,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,5; 59,95</t>
+          <t>50,86; 60,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 47,85</t>
+          <t>36,11; 47,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,17; 46,45</t>
+          <t>34,9; 46,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 49,76</t>
+          <t>38,54; 50,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,34; 59,47</t>
+          <t>51,45; 59,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,3; 42,02</t>
+          <t>34,4; 42,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,51; 45,01</t>
+          <t>37,15; 45,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,35; 51,12</t>
+          <t>43,59; 51,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,45; 58,6</t>
+          <t>52,31; 58,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,46; 44,43</t>
+          <t>32,96; 44,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,63; 46,62</t>
+          <t>36,05; 46,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 46,76</t>
+          <t>34,82; 46,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,35; 60,07</t>
+          <t>50,81; 60,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,68; 44,87</t>
+          <t>34,0; 44,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 47,02</t>
+          <t>35,16; 46,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,21; 52,74</t>
+          <t>41,75; 52,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,8; 63,32</t>
+          <t>54,77; 63,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 42,89</t>
+          <t>35,24; 43,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 44,6</t>
+          <t>36,98; 44,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,13; 48,36</t>
+          <t>40,07; 48,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,8; 60,59</t>
+          <t>53,46; 60,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,03; 35,15</t>
+          <t>26,16; 35,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 34,76</t>
+          <t>27,21; 35,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,91; 36,51</t>
+          <t>26,95; 36,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 49,44</t>
+          <t>11,2; 49,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,27; 42,6</t>
+          <t>27,72; 42,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,31; 38,11</t>
+          <t>25,84; 38,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 45,75</t>
+          <t>29,23; 46,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,17; 62,29</t>
+          <t>50,49; 62,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,01; 35,84</t>
+          <t>27,84; 35,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 34,41</t>
+          <t>27,74; 34,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,0; 37,24</t>
+          <t>29,21; 37,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 51,87</t>
+          <t>14,85; 51,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 26,92</t>
+          <t>21,01; 27,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 27,4</t>
+          <t>21,78; 27,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,9; 32,97</t>
+          <t>27,16; 33,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,02; 44,45</t>
+          <t>37,71; 44,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,18; 32,74</t>
+          <t>25,61; 32,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,01; 39,49</t>
+          <t>32,0; 39,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,85; 42,54</t>
+          <t>34,73; 42,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,56; 78,0</t>
+          <t>47,27; 78,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 28,31</t>
+          <t>23,79; 28,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,96; 31,45</t>
+          <t>27,04; 31,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,54; 36,43</t>
+          <t>31,3; 36,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,17; 62,62</t>
+          <t>43,31; 67,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 23,11</t>
+          <t>13,43; 22,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,06</t>
+          <t>15,89; 23,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,09; 36,6</t>
+          <t>27,49; 36,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,94; 43,23</t>
+          <t>33,7; 43,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,0; 28,3</t>
+          <t>20,11; 28,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 29,92</t>
+          <t>22,86; 29,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,2; 37,41</t>
+          <t>29,11; 37,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,11; 41,74</t>
+          <t>27,18; 41,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 25,29</t>
+          <t>18,92; 24,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 26,29</t>
+          <t>21,22; 26,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 35,34</t>
+          <t>29,72; 35,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,66; 40,63</t>
+          <t>30,47; 40,83</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,01; 36,89</t>
+          <t>24,96; 37,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,49; 33,23</t>
+          <t>21,76; 33,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,25; 36,54</t>
+          <t>24,85; 36,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,9; 65,38</t>
+          <t>42,94; 65,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,98; 26,24</t>
+          <t>21,16; 26,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,69; 28,63</t>
+          <t>22,41; 28,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,89</t>
+          <t>28,59; 35,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,14; 46,22</t>
+          <t>39,32; 46,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,54; 27,75</t>
+          <t>22,58; 27,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 28,44</t>
+          <t>23,08; 28,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,25; 34,71</t>
+          <t>29,02; 34,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,85; 49,34</t>
+          <t>42,06; 49,48</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,75; 30,47</t>
+          <t>26,98; 30,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,87; 31,44</t>
+          <t>27,93; 31,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,97; 36,58</t>
+          <t>33,02; 36,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,46; 47,63</t>
+          <t>32,58; 47,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,65; 30,82</t>
+          <t>27,59; 30,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,52; 32,77</t>
+          <t>29,57; 33,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,31; 38,85</t>
+          <t>35,42; 39,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,97; 60,46</t>
+          <t>45,79; 60,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,66; 30,17</t>
+          <t>27,74; 30,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,23; 31,74</t>
+          <t>29,29; 31,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,9; 37,41</t>
+          <t>34,8; 37,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,64; 51,24</t>
+          <t>41,64; 51,58</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>116761; 154445</t>
+          <t>117099; 154558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>142959; 184769</t>
+          <t>142863; 185362</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174706; 215235</t>
+          <t>173919; 213185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252100; 299250</t>
+          <t>253868; 300948</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98265; 128366</t>
+          <t>96872; 128556</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100431; 136554</t>
+          <t>102577; 136578</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121295; 157140</t>
+          <t>121710; 157925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>226369; 262233</t>
+          <t>226837; 263884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>224494; 275039</t>
+          <t>225185; 275980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251257; 309786</t>
+          <t>255695; 310025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304904; 359616</t>
+          <t>306604; 359495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>493102; 550899</t>
+          <t>491747; 551741</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100461; 133391</t>
+          <t>98962; 133005</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>136723; 178883</t>
+          <t>138339; 180102</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110106; 148068</t>
+          <t>110267; 147201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225801; 269342</t>
+          <t>227846; 272082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>115665; 149662</t>
+          <t>113398; 149017</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>108705; 147413</t>
+          <t>110220; 144701</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>137459; 175915</t>
+          <t>139266; 176059</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>206919; 239096</t>
+          <t>206826; 239625</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>224147; 271807</t>
+          <t>223330; 273635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255199; 310978</t>
+          <t>257837; 311794</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260910; 314472</t>
+          <t>260570; 312305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>444409; 500455</t>
+          <t>441608; 499424</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111991; 151234</t>
+          <t>112571; 151053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>144147; 186125</t>
+          <t>145710; 187952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109048; 147934</t>
+          <t>109213; 147683</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71336; 326668</t>
+          <t>73971; 326688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38192; 59666</t>
+          <t>38829; 60210</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63595; 92103</t>
+          <t>62454; 93397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41300; 63788</t>
+          <t>40755; 64324</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82766; 102755</t>
+          <t>83285; 103893</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159758; 204419</t>
+          <t>158801; 201228</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>217206; 267454</t>
+          <t>215581; 268739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157954; 202815</t>
+          <t>159072; 203630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>129224; 428259</t>
+          <t>122576; 425761</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>182942; 234626</t>
+          <t>183081; 236946</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209078; 265940</t>
+          <t>211378; 266861</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>236605; 289993</t>
+          <t>238874; 294707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>379144; 443245</t>
+          <t>376075; 444526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>149645; 194577</t>
+          <t>152184; 194246</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>223753; 276008</t>
+          <t>223688; 274234</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>238387; 291005</t>
+          <t>237558; 289726</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>456008; 747930</t>
+          <t>453225; 748382</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>348159; 414957</t>
+          <t>348717; 416041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>450201; 525120</t>
+          <t>451401; 528535</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>493081; 569552</t>
+          <t>489399; 567901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>844358; 1224860</t>
+          <t>847170; 1315745</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32684; 57308</t>
+          <t>33290; 56381</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65530; 97030</t>
+          <t>64073; 95597</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115184; 155597</t>
+          <t>116884; 156089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144566; 189708</t>
+          <t>147890; 190658</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91196; 129091</t>
+          <t>91727; 129035</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>153053; 200702</t>
+          <t>153314; 199290</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>162779; 208569</t>
+          <t>162287; 206906</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>212507; 339758</t>
+          <t>221257; 338205</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130544; 178046</t>
+          <t>133218; 174604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227879; 282357</t>
+          <t>227938; 283486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>289033; 347256</t>
+          <t>292065; 351414</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>371586; 509041</t>
+          <t>381774; 511541</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53089; 78291</t>
+          <t>52970; 79791</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47541; 73510</t>
+          <t>48138; 73666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60999; 88270</t>
+          <t>60026; 89230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102369; 152480</t>
+          <t>100146; 153062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>198205; 247896</t>
+          <t>199878; 250337</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>210011; 264953</t>
+          <t>207335; 264609</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>235516; 287913</t>
+          <t>235923; 291078</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>291168; 343862</t>
+          <t>292492; 343560</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>260778; 321013</t>
+          <t>261181; 320234</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>263561; 326121</t>
+          <t>264644; 325237</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>312033; 370303</t>
+          <t>309549; 372037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>408952; 482149</t>
+          <t>410970; 483461</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>654871; 745949</t>
+          <t>660576; 751767</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>810786; 914431</t>
+          <t>812384; 910713</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>875585; 971381</t>
+          <t>877033; 980614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1063843; 1561041</t>
+          <t>1067908; 1563159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>756653; 843521</t>
+          <t>755241; 847017</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>928105; 1030444</t>
+          <t>929685; 1037927</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1008435; 1109481</t>
+          <t>1011514; 1120205</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1609057; 2116298</t>
+          <t>1602819; 2114193</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1434256; 1564606</t>
+          <t>1438277; 1570752</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1769258; 1921187</t>
+          <t>1772970; 1918818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1923295; 2061676</t>
+          <t>1918022; 2058594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2889766; 3473206</t>
+          <t>2822385; 3496077</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,01</t>
+          <t>30,29; 40,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,23; 47,01</t>
+          <t>35,68; 46,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,87; 55,0</t>
+          <t>44,13; 55,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,86; 60,29</t>
+          <t>51,64; 60,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 47,92</t>
+          <t>36,26; 47,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,9; 46,46</t>
+          <t>34,23; 46,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,54; 50,01</t>
+          <t>38,85; 50,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,45; 59,85</t>
+          <t>51,78; 59,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,4; 42,16</t>
+          <t>34,54; 42,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,15; 45,05</t>
+          <t>37,27; 45,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,59; 51,11</t>
+          <t>43,86; 51,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,31; 58,69</t>
+          <t>52,95; 58,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,96; 44,3</t>
+          <t>33,48; 45,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 46,94</t>
+          <t>35,46; 46,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 46,49</t>
+          <t>34,85; 46,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,81; 60,68</t>
+          <t>51,26; 60,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 44,67</t>
+          <t>34,4; 45,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 46,16</t>
+          <t>34,59; 46,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,75; 52,78</t>
+          <t>41,41; 52,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,77; 63,46</t>
+          <t>54,24; 62,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,24; 43,18</t>
+          <t>34,94; 43,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,98; 44,72</t>
+          <t>36,57; 44,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,07; 48,03</t>
+          <t>40,06; 47,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,46; 60,46</t>
+          <t>53,91; 60,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 35,11</t>
+          <t>26,52; 35,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,21; 35,1</t>
+          <t>26,75; 34,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,95; 36,45</t>
+          <t>27,27; 36,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 49,44</t>
+          <t>44,4; 53,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 42,99</t>
+          <t>27,42; 43,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,84; 38,64</t>
+          <t>26,25; 38,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,23; 46,14</t>
+          <t>29,4; 45,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,49; 62,98</t>
+          <t>49,72; 62,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,84; 35,28</t>
+          <t>27,77; 35,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,74; 34,58</t>
+          <t>27,71; 34,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 37,39</t>
+          <t>29,13; 37,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 51,56</t>
+          <t>47,44; 54,96</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,01; 27,19</t>
+          <t>21,07; 26,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,78; 27,49</t>
+          <t>21,72; 27,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,16; 33,51</t>
+          <t>27,0; 33,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,71; 44,58</t>
+          <t>37,5; 44,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 32,68</t>
+          <t>25,0; 32,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,0; 39,24</t>
+          <t>32,13; 39,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,73; 42,36</t>
+          <t>35,0; 42,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,27; 78,05</t>
+          <t>45,61; 51,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 28,38</t>
+          <t>23,53; 28,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,04; 31,66</t>
+          <t>26,7; 31,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,3; 36,32</t>
+          <t>31,42; 36,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,31; 67,27</t>
+          <t>42,2; 46,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 22,74</t>
+          <t>13,03; 23,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,89; 23,7</t>
+          <t>15,92; 23,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,49; 36,71</t>
+          <t>27,27; 36,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,7; 43,44</t>
+          <t>33,03; 42,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,11; 28,29</t>
+          <t>19,56; 27,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,86; 29,71</t>
+          <t>22,79; 29,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 37,11</t>
+          <t>29,19; 37,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,18; 41,55</t>
+          <t>39,9; 45,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 24,8</t>
+          <t>18,27; 25,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 26,39</t>
+          <t>21,19; 26,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 35,76</t>
+          <t>29,57; 35,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,47; 40,83</t>
+          <t>38,07; 43,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,96; 37,6</t>
+          <t>25,07; 37,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 33,3</t>
+          <t>21,64; 33,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,85; 36,94</t>
+          <t>25,34; 38,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,94; 65,63</t>
+          <t>45,22; 66,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,16; 26,5</t>
+          <t>21,15; 26,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,41; 28,59</t>
+          <t>22,58; 28,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,59; 35,27</t>
+          <t>28,61; 35,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,32; 46,18</t>
+          <t>40,31; 47,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,58; 27,68</t>
+          <t>22,62; 27,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,08; 28,37</t>
+          <t>23,17; 28,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,02; 34,87</t>
+          <t>28,61; 34,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,06; 49,48</t>
+          <t>43,18; 50,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,98; 30,7</t>
+          <t>26,73; 30,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,93; 31,31</t>
+          <t>27,79; 31,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,02; 36,92</t>
+          <t>32,89; 36,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,58; 47,69</t>
+          <t>45,27; 49,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,59; 30,95</t>
+          <t>27,42; 30,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 33,01</t>
+          <t>29,46; 32,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,42; 39,23</t>
+          <t>35,4; 39,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,79; 60,4</t>
+          <t>47,26; 50,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,74; 30,29</t>
+          <t>27,62; 30,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,29; 31,7</t>
+          <t>29,2; 31,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,8; 37,35</t>
+          <t>34,72; 37,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,64; 51,58</t>
+          <t>46,8; 49,25</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276367</t>
+          <t>306605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>245602</t>
+          <t>268006</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>521969</t>
+          <t>574611</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>117099; 154558</t>
+          <t>116992; 154658</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>142863; 185362</t>
+          <t>140677; 183075</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173919; 213185</t>
+          <t>171035; 213785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253868; 300948</t>
+          <t>280005; 329607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96872; 128556</t>
+          <t>97276; 128562</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>102577; 136578</t>
+          <t>100629; 135717</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121710; 157925</t>
+          <t>122703; 158804</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>226837; 263884</t>
+          <t>249231; 285810</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225185; 275980</t>
+          <t>226117; 277377</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255695; 310025</t>
+          <t>256515; 311911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>306604; 359495</t>
+          <t>308553; 363510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>491747; 551741</t>
+          <t>541998; 603182</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247718</t>
+          <t>267298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>224004</t>
+          <t>244959</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>471721</t>
+          <t>512258</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98962; 133005</t>
+          <t>100512; 135535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138339; 180102</t>
+          <t>136066; 178064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110267; 147201</t>
+          <t>110368; 146179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227846; 272082</t>
+          <t>245702; 290053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>113398; 149017</t>
+          <t>114753; 151162</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>110220; 144701</t>
+          <t>108449; 146303</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>139266; 176059</t>
+          <t>138149; 175759</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>206826; 239625</t>
+          <t>226668; 263137</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223330; 273635</t>
+          <t>221437; 273896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257837; 311794</t>
+          <t>254961; 309667</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260570; 312305</t>
+          <t>260507; 311413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>441608; 499424</t>
+          <t>483668; 539555</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199977</t>
+          <t>226186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>104185</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>330371</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>112571; 151053</t>
+          <t>114103; 151465</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145710; 187952</t>
+          <t>143224; 186725</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109213; 147683</t>
+          <t>110502; 146585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73971; 326688</t>
+          <t>205974; 248782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38829; 60210</t>
+          <t>38408; 60752</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62454; 93397</t>
+          <t>63453; 92604</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40755; 64324</t>
+          <t>40997; 64101</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83285; 103893</t>
+          <t>91906; 116019</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158801; 201228</t>
+          <t>158407; 202940</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215581; 268739</t>
+          <t>215393; 269188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159072; 203630</t>
+          <t>158668; 203349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122576; 425761</t>
+          <t>307748; 356499</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>448079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>570342</t>
+          <t>407212</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>979809</t>
+          <t>855291</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>183081; 236946</t>
+          <t>183587; 233878</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>211378; 266861</t>
+          <t>210886; 264120</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>238874; 294707</t>
+          <t>237436; 290438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>376075; 444526</t>
+          <t>410572; 487234</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>152184; 194246</t>
+          <t>148556; 194677</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>223688; 274234</t>
+          <t>224555; 276804</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>237558; 289726</t>
+          <t>239412; 290642</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>453225; 748382</t>
+          <t>381673; 434363</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>348717; 416041</t>
+          <t>344860; 413830</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>451401; 528535</t>
+          <t>445747; 524721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>489399; 567901</t>
+          <t>491300; 565260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>847170; 1315745</t>
+          <t>815048; 902457</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167231</t>
+          <t>189880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>294894</t>
+          <t>340155</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>462125</t>
+          <t>530036</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33290; 56381</t>
+          <t>32316; 57231</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64073; 95597</t>
+          <t>64193; 94288</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116884; 156089</t>
+          <t>115930; 154784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147890; 190658</t>
+          <t>168414; 216934</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91727; 129035</t>
+          <t>89230; 126946</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>153314; 199290</t>
+          <t>152860; 200597</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>162287; 206906</t>
+          <t>162741; 207504</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>221257; 338205</t>
+          <t>316635; 364362</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133218; 174604</t>
+          <t>128607; 176223</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227938; 283486</t>
+          <t>227559; 281955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>292065; 351414</t>
+          <t>290613; 352246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>381774; 511541</t>
+          <t>496233; 566004</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>127966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>317768</t>
+          <t>357748</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>445357</t>
+          <t>485714</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52970; 79791</t>
+          <t>53199; 78649</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48138; 73666</t>
+          <t>47862; 73727</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60026; 89230</t>
+          <t>61205; 92454</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100146; 153062</t>
+          <t>102097; 149875</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>199878; 250337</t>
+          <t>199759; 250178</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>207335; 264609</t>
+          <t>208954; 262179</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>235923; 291078</t>
+          <t>236145; 292171</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>292492; 343560</t>
+          <t>330048; 385291</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>261181; 320234</t>
+          <t>261717; 319262</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264644; 325237</t>
+          <t>265719; 325521</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309549; 372037</t>
+          <t>305190; 367183</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>410970; 483461</t>
+          <t>450991; 525419</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1428348</t>
+          <t>1566015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1746034</t>
+          <t>1722267</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3174382</t>
+          <t>3288282</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>660576; 751767</t>
+          <t>654573; 746775</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>812384; 910713</t>
+          <t>808228; 910707</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>877033; 980614</t>
+          <t>873435; 975722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1067908; 1563159</t>
+          <t>1501089; 1625189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>755241; 847017</t>
+          <t>750332; 842986</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>929685; 1037927</t>
+          <t>926307; 1034199</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1011514; 1120205</t>
+          <t>1010963; 1115534</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1602819; 2114193</t>
+          <t>1669645; 1775145</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1438277; 1570752</t>
+          <t>1432226; 1562259</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1772970; 1918818</t>
+          <t>1767352; 1920054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1918022; 2058594</t>
+          <t>1913794; 2054987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2822385; 3496077</t>
+          <t>3205123; 3372937</t>
         </is>
       </c>
     </row>
